--- a/SEA-V_Typography_Audit.xlsx
+++ b/SEA-V_Typography_Audit.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,25 +67,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFB91C1C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="FF92600A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF4C3D99"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FFB9186B"/>
+      <color rgb="FF555555"/>
       <sz val="10"/>
     </font>
     <font>
@@ -99,7 +87,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -126,26 +114,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDE2E2"/>
-        <bgColor rgb="FFFDE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FFFFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E2F5"/>
-        <bgColor rgb="FFE2E2F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5D0E0"/>
-        <bgColor rgb="FFF5D0E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -158,6 +128,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -207,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,36 +218,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -281,16 +248,10 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -659,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -669,21 +630,21 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="62" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SEA-V — Typography &amp; Micro-Detail Audit</t>
+          <t>SEA-V — Typography &amp; Micro-Detail Audit (post-fix)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Governing mechanism: css/core/typography.css loads LAST and forces font-size:14px !important on bare a/button/td/th/p/span/li/label/input plus ~45 named classes, and h3-h6 to 14px/700. A lot of page CSS "drift" below is DECLARED but never actually renders because of this — see the Rendered column. See the Legend tab for full details. Compiled 2026-08-03.</t>
+          <t>Updated 2026-08-03 after working through every Inconsistent/Dead code/Bug row. Fixed rows are now green (Consistent) — either converged to a value already proven live elsewhere on the site, or aligned dead source code to match what typography.css actually renders (zero visual change). Two items are intentionally left as Deferred (grey) rather than forced green — see Notes. Shipped as ASSET_VERSION 362.</t>
         </is>
       </c>
     </row>
@@ -734,7 +695,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5" ht="56" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>A — Font family</t>
@@ -773,11 +734,11 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Single source of truth for the whole app + public pages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
+          <t>Unchanged — single source of truth for the whole app + public pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>A — Font family</t>
@@ -800,27 +761,27 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Arial, Helvetica, sans-serif</t>
+          <t>var(--font-app) (was hardcoded Arial)</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>same (not overridden — these bodies aren't in typography.css's font-family reset list)</t>
+          <t>same — was already rendering var(--font-app) via typography.css, which loads after this file at equal specificity</t>
         </is>
       </c>
       <c r="G6" s="13" t="n"/>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Inconsistent</t>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>Real, live divergence from the app's system-ui stack. Minor, likely predates --font-app.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
+          <t>FIXED: corrected the original audit's own mistake — this was dead code, not live drift. index.css never actually controlled the font; cleaned up the misleading Arial declaration to match reality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>A — Font family</t>
@@ -859,11 +820,11 @@
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>Simulated printed CV document — deliberately its own typography system, confirmed by an in-file comment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
+          <t>Unchanged — simulated printed CV document, deliberately its own typography system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A — Font family</t>
@@ -891,22 +852,22 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>same — genuinely live (nested inside the excluded .cv-document)</t>
         </is>
       </c>
       <c r="G8" s="13" t="n"/>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>Intentional variation</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>A SECOND different font stack inside the CV generator's own exception zone — .cv-document and .cv-seav disagree with each other, not just with the app.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
+          <t>RECLASSIFIED from Inconsistent: confirmed this is a second, deliberately different CV template style (SEA-V-branded template opts into Calibri) rather than drift — left alone to avoid changing the template's intended look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>A — Font family</t>
@@ -945,11 +906,11 @@
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>Monospace for a shareable username/URL — legible-code convention, not a bug.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+          <t>Unchanged — monospace for a shareable username/URL, legible-code convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>B — Page titles (h2)</t>
@@ -957,12 +918,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>13 pages declare 24px/900 (1 declares 22px)</t>
+          <t>All pages, unified</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>achievements/certificates/cv-generator/hobbies/navigation/onboard/payslips/references/seatime/specialist-qual/vessels.css (24px); tenders.css:74 (22px)</t>
+          <t>achievements/certificates/cv-generator/hobbies/navigation/onboard/payslips/references/seatime/specialist-qual/tenders/vessels.css</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -972,187 +933,187 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>24px / 900 (tenders: 22px / 900)</t>
+          <t>var(--font-page-title) / var(--font-weight-title) (was hardcoded 22-24px/900 per page)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>18px / 800 (forced by typography.css:65-77)</t>
+          <t>18px / 800 (unchanged, always forced)</t>
         </is>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>Dead code</t>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>Declared sizes disagree page-to-page but NONE of it renders — every page title is actually 18px/800. Tenders' 22px is the one page that even declared something different, also moot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>B — Page titles (h2)</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Dashboard / Profile</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>pages/dashboard.css:136, profile.css:60</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>.dashboard-shell-head h2, .profile-shell-head h2</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>var(--font-page-title)=18px / 900</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>18px / 800 (weight forced)</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>Dead code</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>These two already declared the correct rendered size, just not the weight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
+          <t>FIXED: 12 files' dead 22-24px/900 declarations changed to reference the same vars typography.css enforces — no visual change, removes misleading dead code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>B — Section headings (h3)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>All pages, unified</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>achievements/hobbies/navigation/onboard/payslips/references/seatime/specialist-qual/tenders/vessels.css</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>[class$="-section-head"] h3</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>14px / 700 (was 17-18px / 700-850 per page)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>14px / 700 (unchanged, always forced)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>FIXED: 10 files' dead declarations aligned to match render. Certificates already had no rule (correctly falls back to default) — left as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>B — Section headings (h3)</t>
+          <t>B — Card headings</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>10 pages declare 17-18px / 700-850</t>
+          <t>Dashboard card title</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>achievements:499, hobbies:103, navigation:85, onboard:98, payslips:210, references:102, seatime:235, specialist-qual:96, tenders:106, vessels:117</t>
+          <t>core/layout.css:948</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>[class$="-section-head"] h3</t>
+          <t>.dash-card h3</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>17-18px / 700-850 (varies by page)</t>
+          <t>14px / 700 / rgba(255,255,255,0.95)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>14px / 700 (forced by typography.css:185-198)</t>
+          <t>same</t>
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>Dead code</t>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Section headings render at the SAME size as body text (14px), differentiated only by weight. All the page-to-page size/weight variety in source is dead. Worth deciding: clean up the dead values, or reconsider whether 14px section headings are too flat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
+          <t>Unchanged — already matched the enforced values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>B — Section headings (h3)</t>
+          <t>B — Card headings</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Certificates has no h3 rule at all</t>
+          <t>Dashboard card title (page override)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>certificates.css:80</t>
+          <t>pages/dashboard.css:1692-1705</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>.cert-section-group &gt; .cert-section-head</t>
+          <t>.dashboard-shell-card .dash-card &gt; h3, .kpi-title, .dashboard-card-headline h3</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>n/a — gap</t>
+          <t>var(--font-section-title) / 800</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>14px / 700 (default, no page-specific styling attempted)</t>
+          <t>14px / 700 (h3 always forced)</t>
         </is>
       </c>
       <c r="G13" s="13" t="n"/>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Inconsistent</t>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Not wrong exactly (falls back to the shared default), but every other page bothered to declare page-specific values (even though dead) — Certificates didn't.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
+          <t>FIXED: --font-section-title was referenced but never defined anywhere (broken variable) — defined it in variables.css at 14px, matching the h3 override. No visual change since h3 was already forced regardless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>B — Card headings</t>
+          <t>C — Label text</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Dashboard card title</t>
+          <t>Dead label classes</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>core/layout.css:948</t>
+          <t>meta-grid-cards.css:93-103,255-264</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>.dash-card h3</t>
+          <t>.vessel-meta-label</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>14px / 700 / rgba(255,255,255,0.95)</t>
+          <t>14px (was 8-11px)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>same (already matches the override)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
+          <t>14px (forced, unchanged)</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="n"/>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Consistent</t>
@@ -1160,97 +1121,97 @@
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>The one heading class that was already written at the values typography.css enforces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
+          <t>FIXED: declared size aligned to match what typography.css already forces (these classes are on its named list).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>B — Card headings</t>
+          <t>C — Label text</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dashboard card title (page override)</t>
+          <t>KPI box labels — unified</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>pages/dashboard.css:1692-1705</t>
+          <t>dashboard.css, achievements.css, hobbies-interests.css, seatime.css</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>.dashboard-shell-card .dash-card &gt; h3, .kpi-title, .dashboard-card-headline h3</t>
+          <t>.kpi-label variants</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>font-size: var(--font-section-title) [undefined] / weight 800</t>
+          <t>11px / 800 (was 700-800, one page at 10px)</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>14px / 700 (var falls through to nothing, weight forced)</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>Bug</t>
+          <t>same (live — div elements, not overridden)</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>--font-section-title is referenced but never defined anywhere — dead/broken custom property. Harmless only because the global override masks it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+          <t>FIXED: converged dashboard (850→800) and achievements (700→800) to the majority convention. Seatime's 10px in the OOW panel is a documented deliberate compact-footprint exception (comment already explains it) — left alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>C — Label text</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>3 classes with SMALL declared sizes, all overridden</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>meta-grid-cards.css:93-103,255-264; dashboard.css:1063-1080,982-987</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>.vessel-meta-label, .dashboard-info-label (incl. profile-top variant)</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>8-11px / 800 / #5bbcff, uppercase</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>14px (forced; uppercase+letter-spacing also stripped by a separate blanket rule)</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>Dead code</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Intended a compact blue uppercase label, actually renders as plain 14px.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Vessels page labels — unified</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>vessels.css:289-297,413-429,599-607</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>.vessel-section-label, .vessel-panel-label, .vessel-specs-grid span</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>11px / 800 (was 800-950 across 3 different rules)</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>same (live)</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>FIXED: all three converged to the same 11px/800 KPI-label convention used site-wide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>C — Label text</t>
@@ -1258,42 +1219,42 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>KPI box labels — LIVE, and inconsistent with each other</t>
+          <t>CV Generator field label</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>dashboard.css:1163-1174; achievements.css:96-103; hobbies-interests.css:91-97; seatime.css:741-743</t>
+          <t>cv-generator.css:191-198</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>.kpi-label variants</t>
+          <t>.cvgen-field-label</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>10-11px / 700-800</t>
+          <t>11px / 800 (was 850)</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>10-11px / 700-800 (NOT overridden — these class names aren't on typography.css's list)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="n"/>
+          <t>same (live)</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="n"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Inconsistent</t>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>These actually render as declared, and they don't all agree: 11px/700 (dashboard, achievements) vs 11px/800 (hobbies) vs 10px/700 (seatime).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1">
+          <t>FIXED: weight converged to match the site convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>C — Label text</t>
@@ -1301,558 +1262,558 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Vessels page labels — LIVE, own micro-scale</t>
+          <t>Navigation stat label</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>vessels.css:289-297,413-429,599-607,847-868</t>
+          <t>navigation.css:157-165</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>.vessel-section-label (12px/950), .vessel-panel-label (12px/850), .vessel-specs-grid span (11px/800), .vessel-total-row (12px/800)</t>
+          <t>.navigation-stat-label</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>11-12px / 800-950</t>
+          <t>11px / 800 / #5bbcff (was 10px, muted white)</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>same (not overridden)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="n"/>
+          <t>same (live)</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="n"/>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Inconsistent</t>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>Four different label weights within ONE page's own component family.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>C — Label text</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>CV Generator field label — LIVE</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>cv-generator.css:191-198</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>.cvgen-field-label</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>11px / 850 / #5bbcff</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>same (not overridden)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Close to but not identical to the Vessels/KPI conventions above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
+          <t>FIXED: was the one label anywhere on the site that broke the shared blue convention — converged to match .navigation-route-label's own pattern in the same file. Checked for a legibility reason first (highlight background) — none found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>C — Value text</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard info value</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>dashboard.css:1082-1087,989-993, 1734-1743</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>.dashboard-info-value + --font-value usages</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>14px (was 11-14px, one broken var)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>14px (forced / defined)</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>FIXED: --font-value was undefined (broken variable, silently falling back to inherited size on .dashboard-shell-card contexts) — defined at 14px in variables.css, matching the site's value convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>C — Label text</t>
+          <t>C — Value text</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Navigation stat label — breaks the blue-label convention</t>
+          <t>Vessel main/stats/specs value — unified</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>navigation.css:157-165</t>
+          <t>vessels.css:431-439,609-618</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>.navigation-stat-label</t>
+          <t>.vessel-main-item strong, .vessel-stats-grid strong, .vessel-specs-grid strong</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>10px / 800 / rgba(255,255,255,0.58) — muted white, not blue</t>
+          <t>14px / 700 (was 500-600 weight, one at 13px)</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>14px (overridden on size only — color still renders muted white)</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n"/>
+          <t>same (live)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="n"/>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Inconsistent</t>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>The one "label" anywhere on the site that isn't the shared blue — every other label above uses #5bbcff or a var defaulting to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+          <t>FIXED: converged to the site's 14px/700 value convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>C — Value text</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Dashboard info value</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>dashboard.css:1082-1087,989-993</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>.dashboard-info-value (+ profile-top variant)</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>11-14px / 700 / rgba(255,255,255,0.94)</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>14px (forced where declared smaller)</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="n"/>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>Dead code</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>profile-top variant declared 11px, dead; main variant already matched 14px.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>C — Value text</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Vessel main/stats value — LIVE, lighter weight</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>vessels.css:431-439</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>.vessel-main-item strong, .vessel-stats-grid strong</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>14px / 500</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>same (not overridden)</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Lower font-weight (500) than every other "value" convention on the site (which cluster around 600-700).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Navigation stat value</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>navigation.css:149-155</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>.navigation-stat-value</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>18px / 900 / #fff</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>same (live)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>Intentional variation</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>RECLASSIFIED from Inconsistent: confirmed via navigation.html this powers 6 standalone headline stats (Total NM, % of Earth's circumference, etc.) — a genuine large-stat callout akin to a KPI number, not a routine field value. Left unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>C — Muted/secondary text</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>301 declarations, 39 distinct alpha values</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>scattered across every css/pages/*.css file</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>color: rgba(255,255,255,0.XX)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0.05 to 0.95</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>NOT touched this pass. Consolidating 301 hand-picked opacity values into a small token set is a real design decision (risk of flattening deliberate visual hierarchy), not a mechanical fix — too large/risky to safely batch alongside everything else. Recommend a dedicated follow-up pass if you want this tackled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>C — Value text</t>
+          <t>C — Muted/secondary text</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Vessel specs value — LIVE</t>
+          <t>--muted / --muted2 — defined, unused</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>vessels.css:609-618</t>
+          <t>core/variables.css:28-29</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>.vessel-specs-grid strong</t>
+          <t>:root</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>13px / 600 / rgba(255,255,255,0.88)</t>
+          <t>--muted: rgba(255,255,255,0.82); --muted2: rgba(255,255,255,0.68)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>same (not overridden)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G23" s="22" t="n"/>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>13px instead of the site's flat 14px body size, and a slightly dimmer white than pure #fff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>C — Value text</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Navigation stat value — LIVE, oversized</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>navigation.css:149-155</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>.navigation-stat-value</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>18px / 900 / #fff</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>same (not overridden)</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Noticeably larger than every other inline "value" — closer to a KPI-number treatment than a field value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>C — Muted/secondary text</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>301 declarations, 39 distinct alpha values</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>scattered across every css/pages/*.css file</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>color: rgba(255,255,255,0.XX)</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>0.05 to 0.95 (see distribution below)</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>n/a — 39 different values</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="24" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>Top 5 most-used: 0.55 (26), 0.78 (25), 0.72 (24), 0.68 (22), 0.60 (22). Full per-line list available on request — too long for one spreadsheet row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>C — Muted/secondary text</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>--muted / --muted2 variables — defined, unused</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>core/variables.css:28-29</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>:root</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>--muted: rgba(255,255,255,0.82); --muted2: rgba(255,255,255,0.68)</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
+          <t>Left as-is (harmless, available for future use) rather than force-wiring them into the 301 declarations above without knowing which ones they're meant to replace — same reasoning as the row above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>D — Collapsible group titles</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Standard pattern — unified</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>seatime.css, tenders.css, navigation.css, public-profile.css, payslips.css</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>.xxx-vessel-group-title strong / small, .ps-year-summary-title</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>strong: #fff 14px/800; small: rgba(255,255,255,0.5) 11px/600 (all 5 files now match)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>same (live)</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>FIXED: Payslips was 1px larger on both title/subtitle plus a slightly higher muted alpha — converged to match Seatime/Tenders/Navigation/Achievements exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>D — Collapsible group titles</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Onboard Experience — different naming convention</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>onboard-experience.css, public-profile.css</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G26" s="25" t="n"/>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Built specifically to solve this problem and never referenced anywhere — confirmed 0 usages of var(--muted) or var(--muted2) in the whole css/ tree. Every muted-text declaration hardcodes its own value instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>D — Collapsible group titles</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Standard pattern (4 of 5 match exactly)</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>seatime.css:423-447, tenders.css:184-208, navigation.css:833-853, public-profile.css:731-751</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>.xxx-vessel-group-title strong / small</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>strong: #fff 14px/800; small: rgba(255,255,255,0.5) 11px/600</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>same (live, not overridden — these are span/strong inside a header, strong itself isn't in the override list)</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="n"/>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Consistent</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Seatime, Tenders, Navigation, and Achievements(public profile) are byte-for-byte identical.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>doesn't follow the -group-title strong/small pattern</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>NOT touched — this is a structural class-naming difference, not a visual bug, and renaming would touch classes referenced across JS. Left alone; flag if you want it unified to the shared naming convention in a future pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>E — Buttons</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Pill/status-pill family</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>core/variables.css:171-181, components/pills.css</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>.pill, .status-pill, .cert-status-pill, etc.</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>12px / 800 / letter-spacing 0.2px</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>same — live</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>E — Buttons</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>.seav-action — used on nearly every card site-wide</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>components/actions.css:29-58, core/typography.css</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Edit/Delete/View buttons on every page</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>12px / 800 (pill-sized, as originally declared)</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>12px / 800 — NOW LIVE (was silently rendering 14px)</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>FIXED — the single highest-impact change in this batch. Added .seav-action to typography.css's pill-exemption list (the same mechanism status pills already use). Edit/Delete/View buttons everywhere now render at their originally-intended compact pill size instead of the accidentally-inflated 14px. This is the one item most worth eyeballing on a few pages before calling it done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>D — Collapsible group titles</t>
+          <t>E — Buttons</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Payslips outlier</t>
+          <t>.btn-blue / .btn-ghost2 — primary buttons site-wide</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>payslips.css:285-306</t>
+          <t>components/buttons.css:27-46, core/typography.css</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>.ps-year-summary-title strong / small</t>
+          <t>primary Save/Add/Submit-style buttons</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>strong: #fff 15px/800; small: rgba(255,255,255,0.55) 12px/600</t>
+          <t>12px / 800 (pill-sized, as originally declared)</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>same (live)</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="n"/>
+          <t>12px / 800 — NOW LIVE (was silently rendering 14px)</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n"/>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Inconsistent</t>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>1px larger on both title and subtitle than the other four, plus a slightly higher muted alpha (0.55 vs 0.5).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="48" customHeight="1">
+          <t>FIXED — same mechanism/reasoning as .seav-action above. Also worth a visual check since it affects primary buttons broadly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>D — Collapsible group titles</t>
+          <t>E — Buttons</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Onboard Experience — different naming convention</t>
+          <t>.btn-attach</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>onboard-experience.css (.onboard-vessel-summary-left), public-profile.css (.public-onboard-vessel-group)</t>
+          <t>components/buttons.css:106-118</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>attachment upload buttons</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>doesn't follow the -group-title strong/small pattern at all</t>
+          <t>12px (pill-sized; was declaring 11px, dead)</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>12px — now live via the same exemption</t>
         </is>
       </c>
       <c r="G29" s="13" t="n"/>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Inconsistent</t>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>Structural naming outlier, not just a value mismatch — two more different conventions layered on top of the 5 already found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+          <t>FIXED alongside the two above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>E — Buttons</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Pill/status-pill family — the only thing that renders as declared</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>core/variables.css:171-181, components/pills.css</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>.pill, .status-pill, .cert-status-pill, etc. (explicit exclusion list in typography.css:161-180)</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>12px / 800 / letter-spacing 0.2px</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>same — genuinely live</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Consistent</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>This is the ONE place the intended pill typography convention actually renders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="48" customHeight="1">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>.btn-danger</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>components/buttons.css:79-90</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>delete/destructive buttons</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>14px / 600 (unchanged)</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>same (weight always live)</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>Intentional variation</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>RECLASSIFIED from Inconsistent: this is a structurally different button tier (30px radius, not a 999px pill) from the .seav-action/.btn-blue pill family — left its own weight alone rather than force a mismatch with its own shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>E — Buttons</t>
@@ -1860,499 +1821,210 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>.btn-blue / .btn-ghost2</t>
+          <t>.form-button</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>components/buttons.css:27-46</t>
+          <t>components/forms.css:51-70</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>shared button classes</t>
+          <t>form submit buttons</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>var(--pill-font-size)=12px / 800 / letter-spacing 0.2px</t>
+          <t>14px / 700 (unchanged)</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>14px / 800 / letter-spacing normal (forced — explicitly listed)</t>
+          <t>same (weight always live)</t>
         </is>
       </c>
       <c r="G31" s="13" t="n"/>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>Dead code</t>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>Intentional variation</t>
         </is>
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>Declares the pill convention, never renders it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>E — Buttons</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>.seav-action — used on nearly every card site-wide</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>components/actions.css:29-58</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Edit/Delete/View buttons on Certificates, Payslips, SpecialistQuals, Navigation, Tenders, Seatime, Onboard, References, Achievements</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>12px / 800 / letter-spacing 0.2px</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>14px / letter-spacing normal (forced — bare &lt;a&gt; is in the override list)</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>Dead code</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>HIGHEST-IMPACT finding in this category: this is the single most-reused action button in the app, and its intended compact sizing never renders anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="48" customHeight="1">
+          <t>RECLASSIFIED from Inconsistent: another distinct tier (46px height, 22px radius) — same reasoning as .btn-danger above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>F — Redundant count badges</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Standard badge — unified</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>seatime.css, tenders.css, navigation.css, public-profile.css, payslips.css</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>.xxx-vessel-group-count, .ps-year-summary-count</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>11px / 800 / 22px min-width / 1px 8px padding (all 5 files now match)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>same (live)</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>FIXED: Payslips was measurably larger (12px/26px/3px-9px) — converged to match the other four. Background color still varies intentionally by page accent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>E — Buttons</t>
+          <t>F — Redundant count badges</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>.btn-attach</t>
+          <t>Duplicate count in text + badge</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>components/buttons.css:106-118</t>
+          <t>seatime.js, tenders.js, navigation-list.js, public-profile-sections.js (×2), payslips-render.js</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>attachment upload buttons</t>
+          <t>collapsible group headers</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>11px, no explicit weight</t>
+          <t>count shown once (badge only)</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>14px (forced)</t>
+          <t>was shown twice (e.g. "7 entries" text + a separate "7" badge)</t>
         </is>
       </c>
       <c r="G33" s="13" t="n"/>
-      <c r="H33" s="18" t="inlineStr">
-        <is>
-          <t>Dead code</t>
-        </is>
-      </c>
-      <c r="I33" s="15" t="inlineStr"/>
-    </row>
-    <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>E — Buttons</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>.btn-danger — weight is genuinely live</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>components/buttons.css:79-90</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>delete/destructive buttons</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>no explicit size (14px forced) / weight 600</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>14px / 600 (weight NOT touched by the override — only size is)</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>The only button whose declared weight (600) is real and differs from the 800 pill convention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="48" customHeight="1">
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>FIXED across all 5 files: removed the redundant number from the descriptive text, kept genuinely distinct info where it existed (qualifying days, months logged, total NM) and dropped the small-text line entirely where it had nothing but the repeated count. No computation changed, only what's displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>G — Dashboard snippets</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Sea Time / Certificates / References preview cards</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>js/dashboard-snippets.js, css/pages/dashboard.css</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>#dashSeatimeSnippet, #dashCertSnippet, #dashRefSnippet</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>new .dash-snippet-row cards matching each page's current colors/borders/pills</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>was an old flat &lt;table&gt; (Seatime) or uppercase .list-row (Certificates/References)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>FIXED conservatively per your request: only the wrapping markup/CSS classes changed. All underlying data-fetching, sorting, truncation, verification-status and expiry-status logic in dashboard-snippets.js is untouched — same computations, just restyled to match the redesigned pages instead of the old generic table/list look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>E — Buttons</t>
+          <t>G — Dashboard snippets</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>.form-button — weight is genuinely live</t>
+          <t>Vessels/Tenders/SpecialistQuals/Onboard/Hobbies</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>components/forms.css:51-70</t>
+          <t>js/dashboard-snippets.js</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>form submit buttons</t>
+          <t>already used the shared js/seav-cards.js builders</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>no explicit size (14px forced) / weight 700</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>14px / 700 (weight live)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G35" s="13" t="n"/>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Inconsistent</t>
+          <t>Consistent</t>
         </is>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>A third distinct button weight (700) — so the site has THREE different live button weights in play: 600 (danger), 700 (form), 800 (true pills), despite one being the "intended" convention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>F — Redundant count badges</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Standard badge (4 of 5 match)</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>seatime.css:449-465, tenders.css:210-226, navigation.css:855-866, public-profile.css:753-764</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>.xxx-vessel-group-count</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>11px / 800 / white text / 999px pill / 1px 8px padding / 22px min-width</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>same (live)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>Consistent</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Background color varies intentionally by page accent (green for Seatime/Tenders/Achievements, blue for Navigation) — that's by design, not drift.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="48" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>F — Redundant count badges</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Payslips badge outlier</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>payslips.css:308-318</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>.ps-year-summary-count</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>12px / 800 / white / 999px pill / 3px 9px padding / 26px min-width</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>same (live)</t>
-        </is>
-      </c>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>Measurably larger than the other four — consistent with Payslips also being the Category D title/subtitle outlier. Looks like this component was built at a slightly different scale from the shared pattern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>F — Redundant count badges</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>The redundancy itself (count shown twice)</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>all 5 files above</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>small subtitle text + separate count badge, same number</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>e.g. "7 entries • 494 qualifying days" AND a circular "7" badge</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>This is a content/UX repetition across all 5 instances, not a styling mismatch — flagged separately from the badge styling itself so it can be decided on its own (e.g. drop the badge, or drop the count from the text).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>G — Dashboard snippets</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Seatime snippet — stale</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>js/dashboard-snippets.js:80-143</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>renderSeatimeSnippet()</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>generic table.css convention (12px th, uppercase, --surface-bg-soft wrapper)</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Seatime page itself has moved to vessel-grouped collapsible cards (seatime.css) — snippet never followed</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="24" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Header color/background were actually hand-matched to the new page (per an in-file comment), but the STRUCTURE (flat table vs grouped collapsible cards) never was.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>G — Dashboard snippets</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Certificates snippet — stale</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>js/dashboard-snippets.js:155</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>renderCertSnippet()</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>generic .list/.list-row convention</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>Certificates page uses .cert-compact-card collapsible cards with issuer/expiry pills</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I40" s="15" t="inlineStr"/>
-    </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>G — Dashboard snippets</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>References snippet — stale</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>js/dashboard-snippets.js:824</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>renderReferenceSnippet()</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>generic .list/.list-row convention</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>References page uses .reference-modern-card, sectioned with large attachment previews</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="I41" s="15" t="inlineStr"/>
-    </row>
-    <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>G — Dashboard snippets</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>Vessels/Tenders/SpecialistQuals/Onboard/Hobbies — in sync</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>js/dashboard-snippets.js (5 functions)</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>renderVesselSnippet, renderTenderSnippet, renderSpecialistSnippet, renderOnboardSnippet, renderHobbiesSnippet</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>window.SeavCards.build*() shared builder</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>same page style automatically, via the shared js/seav-cards.js module</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="26" t="inlineStr">
-        <is>
-          <t>Consistent</t>
-        </is>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>The fix pattern already exists in the codebase — Seatime/Certificates/References are the only 3 snippets that never got migrated onto it.</t>
+          <t>Unchanged — already correct.</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2379,90 +2051,65 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Status meaning</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>Consistent</t>
-        </is>
-      </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>Matches its own convention and matches other equivalent components. No action needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>Inconsistent</t>
-        </is>
-      </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>Genuinely renders differently from equivalent components elsewhere — a real visual mismatch, live on screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Matches its own convention and matches other equivalent components (fixed or already correct). No action needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Intentional variation</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Differs on purpose (CV document typography, monospace share fields, etc.) — not drift.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>Dead code</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>Declared in CSS but overridden by typography.css's blanket rules — doesn't actually affect what renders. Safe to leave, but confusing for future edits and worth a cleanup pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>Broken source: an undefined CSS variable, an unused variable that should have been the fix, or similar. Currently harmless only by accident.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>The governing mechanism</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="170" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>css/core/typography.css is imported LAST in styles.css (after every page/component file), and its two main blocks use :where(...) selector lists with font-size: var(--font-body) !important (14px). Block 1 (lines 90-158) covers bare a/button/td/th/p/span/li/label/input/select/textarea plus ~45 named classes. Block 2 (lines 185-198) covers h3/h4/h5/h6 and any [class$="-section-head"] h3, forcing 14px/700. A third block (lines 64-77) forces page-title h2s to 18px/800. A fourth block (lines 161-180) explicitly EXEMPTS pill/badge classes so they keep their intended 12px sizing.
-Net effect: a large amount of the font-size variety you'd find reading page CSS files in isolation is dead code — declared but never rendered. This spreadsheet's "Declared value" vs "Actually renders" columns separate the two, so real visual inconsistencies (Inconsistent) aren't confused with harmless-but-confusing source code (Dead code).</t>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Differs on purpose (CV template styles, monospace share fields, large stat readouts, different button-shape tiers) — not drift, confirmed by checking context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Left untouched on purpose — either too large/risky to safely batch in this pass (the 301-value muted-text sprawl) or a structural naming difference with no visual impact. Flagged for a dedicated follow-up if you want it addressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>What shipped in this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="110" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>ASSET_VERSION bumped to 362, patch-html-scripts.mjs re-run (25 files patched), full eslint pass clean, CSS brace-balance check clean across all 45 files. Biggest visible change: .seav-action / .btn-blue / .btn-ghost2 / .btn-attach now render at their originally-declared 12px pill size instead of an accidentally-inflated 14px (added to the same pill-exemption mechanism status pills already use in typography.css) — worth a specific look on a few pages. Everything else converges existing declared values to a convention already proven live elsewhere on the site, or corrects source code that never affected rendering.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
